--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484135_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484135_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7974</v>
+        <v>2.9395</v>
       </c>
       <c r="E2" t="n">
-        <v>5.113</v>
+        <v>5.9745</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.3156</v>
+        <v>-3.035</v>
       </c>
       <c r="G2" t="n">
         <v>3.075</v>
@@ -610,13 +610,13 @@
         <v>2.579</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.2615</v>
+        <v>-1.1194</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5586</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7029</v>
+        <v>-0.4223</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6032</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7668</v>
+        <v>1.9816</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4624</v>
+        <v>4.1823</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6956</v>
+        <v>-2.2006</v>
       </c>
       <c r="G3" t="n">
         <v>-0.5205</v>
@@ -688,13 +688,13 @@
         <v>2.3806</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.161</v>
+        <v>0.0539</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8047</v>
+        <v>-0.0849</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6438</v>
+        <v>0.1388</v>
       </c>
       <c r="V3" t="n">
         <v>0.266</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.4047</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.06370000000000001</v>
+        <v>0.0383</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4711</v>
+        <v>-0.4431</v>
       </c>
       <c r="G4" t="n">
         <v>-1.16</v>
@@ -766,13 +766,13 @@
         <v>0.5952</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0301</v>
+        <v>0.1601</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1643</v>
+        <v>-0.0623</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1944</v>
+        <v>0.2224</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1688</v>
+        <v>-1.0682</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2969</v>
+        <v>-0.3366</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8719</v>
+        <v>-0.7317</v>
       </c>
       <c r="G5" t="n">
         <v>-3.8515</v>
@@ -844,13 +844,13 @@
         <v>1.1903</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5357</v>
+        <v>0.6363</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2778</v>
+        <v>0.2381</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2579</v>
+        <v>0.3981</v>
       </c>
       <c r="V5" t="n">
         <v>2.1469</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3919</v>
+        <v>-1.3321</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9591</v>
+        <v>-0.5907</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4328</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>2.3103</v>
@@ -922,13 +922,13 @@
         <v>1.1903</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4801</v>
+        <v>0.5399</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3514</v>
+        <v>0.0171</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8314</v>
+        <v>0.5228</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2065</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.346</v>
+        <v>-1.9394</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2794</v>
+        <v>-0.013</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0667</v>
+        <v>-1.9264</v>
       </c>
       <c r="G7" t="n">
         <v>-1.244</v>
@@ -1000,13 +1000,13 @@
         <v>1.7855</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0741</v>
+        <v>-0.6674</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6858</v>
+        <v>-0.4194</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3883</v>
+        <v>-0.248</v>
       </c>
       <c r="V7" t="n">
         <v>-1.615</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. ACOSTA ALMONTE</t>
+          <t>A. IGLESIAS GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.6479</v>
+        <v>-4.1778</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0359</v>
+        <v>-4.1615</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.612</v>
+        <v>-0.0163</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.7934</v>
+        <v>-4.0318</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.6858</v>
+        <v>-1.2451</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1076</v>
+        <v>-2.7867</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.277</v>
+        <v>-1.7186</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.4778</v>
+        <v>-0.5189</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2008</v>
+        <v>-1.1997</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.5164</v>
+        <v>-2.3132</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.208</v>
+        <v>-0.7262</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3084</v>
+        <v>-1.587</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5952</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9919</v>
+        <v>-2.1822</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>1.8876</v>
+        <v>0.2508</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5703</v>
+        <v>-0.2607</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3173</v>
+        <v>0.5115</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. IGLESIAS GARCIA</t>
+          <t>D. ACOSTA ALMONTE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.0766</v>
+        <v>-4.6229</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.1445</v>
+        <v>-3.0109</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0679</v>
+        <v>-1.612</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.0318</v>
+        <v>-5.7934</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2451</v>
+        <v>-4.6858</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.7867</v>
+        <v>-1.1076</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7186</v>
+        <v>-2.277</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5189</v>
+        <v>-2.4778</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1997</v>
+        <v>0.2008</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3132</v>
+        <v>-3.5164</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7262</v>
+        <v>-2.208</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.587</v>
+        <v>-1.3084</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1822</v>
+        <v>-0.9919</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7855</v>
+        <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>0.352</v>
+        <v>0.9126</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2436</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5956</v>
+        <v>0.3173</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4885</v>
+        <v>-5.0756</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6941</v>
+        <v>-1.3654</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.7943</v>
+        <v>-3.7102</v>
       </c>
       <c r="G10" t="n">
         <v>-4.5139</v>
@@ -1234,13 +1234,13 @@
         <v>1.5871</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6807</v>
+        <v>-0.2678</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2323</v>
+        <v>0.0965</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4484</v>
+        <v>-0.3642</v>
       </c>
       <c r="V10" t="n">
         <v>-1.881</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.524</v>
+        <v>-5.3563</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5565</v>
+        <v>-2.6132</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9676</v>
+        <v>-2.7431</v>
       </c>
       <c r="G11" t="n">
         <v>-7.1693</v>
@@ -1312,13 +1312,13 @@
         <v>2.1822</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7514999999999999</v>
+        <v>-0.5838</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1869</v>
+        <v>-0.2436</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5646</v>
+        <v>-0.3402</v>
       </c>
       <c r="V11" t="n">
         <v>1.2065</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-20.6143</v>
+        <v>-19.0559</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4547</v>
+        <v>-1.896199999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>-17.1597</v>
+        <v>-17.1598</v>
       </c>
       <c r="G12" t="n">
         <v>-22.8991</v>
@@ -1390,10 +1390,10 @@
         <v>16.8628</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6433</v>
+        <v>-0.08479999999999982</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.3795</v>
+        <v>-0.821</v>
       </c>
       <c r="U12" t="n">
         <v>0.7362000000000002</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. SARRATE CARRILLO</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5634</v>
+        <v>6.9599</v>
       </c>
       <c r="E13" t="n">
-        <v>6.7511</v>
+        <v>3.7683</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1877</v>
+        <v>3.1916</v>
       </c>
       <c r="G13" t="n">
-        <v>6.3711</v>
+        <v>5.1555</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4077</v>
+        <v>0.6755</v>
       </c>
       <c r="I13" t="n">
-        <v>5.9634</v>
+        <v>4.48</v>
       </c>
       <c r="J13" t="n">
-        <v>7.5223</v>
+        <v>5.0558</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0537</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>6.4686</v>
+        <v>4.4605</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1511</v>
+        <v>0.0997</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.646</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5051</v>
+        <v>0.0195</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9838</v>
+        <v>-2.1822</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7935</v>
+        <v>2.1822</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1166</v>
+        <v>-0.0765</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9467</v>
+        <v>-0.3117</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1699</v>
+        <v>0.2352</v>
       </c>
       <c r="V13" t="n">
-        <v>0.266</v>
+        <v>1.881</v>
       </c>
       <c r="W13" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>P. SARRATE CARRILLO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3291</v>
+        <v>6.4699</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6663</v>
+        <v>6.2409</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6628</v>
+        <v>0.2289</v>
       </c>
       <c r="G14" t="n">
-        <v>5.1555</v>
+        <v>6.3711</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6755</v>
+        <v>0.4077</v>
       </c>
       <c r="I14" t="n">
-        <v>4.48</v>
+        <v>5.9634</v>
       </c>
       <c r="J14" t="n">
-        <v>5.0558</v>
+        <v>7.5223</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5953000000000001</v>
+        <v>1.0537</v>
       </c>
       <c r="L14" t="n">
-        <v>4.4605</v>
+        <v>6.4686</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0997</v>
+        <v>-1.1511</v>
       </c>
       <c r="N14" t="n">
-        <v>0.08019999999999999</v>
+        <v>-0.646</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0195</v>
+        <v>-0.5051</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1822</v>
+        <v>-1.9838</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1822</v>
+        <v>0.7935</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7074</v>
+        <v>1.0231</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4137</v>
+        <v>0.4365</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2937</v>
+        <v>0.5865</v>
       </c>
       <c r="V14" t="n">
-        <v>1.881</v>
+        <v>0.266</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2607</v>
+        <v>4.6035</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5643</v>
+        <v>4.3603</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6964</v>
+        <v>0.2432</v>
       </c>
       <c r="G15" t="n">
         <v>1.9896</v>
@@ -1624,13 +1624,13 @@
         <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4776</v>
+        <v>0.8204</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1418</v>
+        <v>-0.0623</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3358</v>
+        <v>0.8827</v>
       </c>
       <c r="V15" t="n">
         <v>0.6032</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2698</v>
+        <v>3.2341</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0684</v>
+        <v>1.8643</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2014</v>
+        <v>1.3698</v>
       </c>
       <c r="G16" t="n">
         <v>4.9491</v>
@@ -1702,13 +1702,13 @@
         <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8321</v>
+        <v>0.7963</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3912</v>
+        <v>0.1871</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4409</v>
+        <v>0.6092</v>
       </c>
       <c r="V16" t="n">
         <v>0.266</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>S. NDOUR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6136</v>
+        <v>2.198</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0128</v>
+        <v>1.1317</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6009</v>
+        <v>1.0663</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3772</v>
+        <v>0.4443</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5147</v>
+        <v>-1.4563</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1375</v>
+        <v>1.9006</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0184</v>
+        <v>0.8312</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2984</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2801</v>
+        <v>1.486</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3588</v>
+        <v>-0.387</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2163</v>
+        <v>-0.8016</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1425</v>
+        <v>0.4146</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3887</v>
+        <v>1.5871</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>1.5871</v>
       </c>
       <c r="S17" t="n">
-        <v>0.717</v>
+        <v>0.6986</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1928</v>
+        <v>0.3004</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5242</v>
+        <v>0.3981</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8692</v>
+        <v>-0.532</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8692</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. NDOUR</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5984</v>
+        <v>2.0567</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3358</v>
+        <v>0.6046</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2627</v>
+        <v>1.4521</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4443</v>
+        <v>1.3772</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4563</v>
+        <v>2.5147</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9006</v>
+        <v>-1.1375</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8312</v>
+        <v>1.0184</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6546999999999999</v>
+        <v>2.2984</v>
       </c>
       <c r="L18" t="n">
-        <v>1.486</v>
+        <v>-1.2801</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.387</v>
+        <v>0.3588</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8016</v>
+        <v>0.2163</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4146</v>
+        <v>0.1425</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5871</v>
+        <v>1.3887</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R18" t="n">
         <v>1.5871</v>
       </c>
       <c r="S18" t="n">
-        <v>1.099</v>
+        <v>0.1601</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5044999999999999</v>
+        <v>-0.2153</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5945</v>
+        <v>0.3754</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.532</v>
+        <v>-0.8692</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.532</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1995</v>
+        <v>1.9979</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5907</v>
+        <v>1.8968</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3912</v>
+        <v>0.1011</v>
       </c>
       <c r="G19" t="n">
         <v>3.5829</v>
@@ -1936,13 +1936,13 @@
         <v>0.7935</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8962</v>
+        <v>-0.0978</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5498</v>
+        <v>-0.2437</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3464</v>
+        <v>0.1459</v>
       </c>
       <c r="V19" t="n">
         <v>2.6789</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6569</v>
+        <v>1.3754</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0901</v>
+        <v>0.216</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7471</v>
+        <v>1.1594</v>
       </c>
       <c r="G20" t="n">
         <v>0.2857</v>
@@ -2014,13 +2014,13 @@
         <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8984</v>
+        <v>-0.18</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4874</v>
+        <v>-0.1813</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.411</v>
+        <v>0.0014</v>
       </c>
       <c r="V20" t="n">
         <v>0.6745</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1811</v>
+        <v>-0.0476</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4873</v>
+        <v>0.7934</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6684</v>
+        <v>-0.8409</v>
       </c>
       <c r="G21" t="n">
         <v>0.545</v>
@@ -2092,13 +2092,13 @@
         <v>0.5952</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3496</v>
+        <v>0.4831</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4761</v>
+        <v>-0.17</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8257</v>
+        <v>0.6531</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4724</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. RIU GARCIA</t>
+          <t>V. VINÓS ALTEMIR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6523</v>
+        <v>-2.9885</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4552</v>
+        <v>-2.4653</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1972</v>
+        <v>-0.5231</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5943</v>
+        <v>-0.2068</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9427</v>
+        <v>0.1806</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6516</v>
+        <v>-0.3875</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0188</v>
+        <v>0.7541</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6197</v>
+        <v>0.2218</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3991</v>
+        <v>0.5323</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5756</v>
+        <v>-0.9609</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.323</v>
+        <v>-0.0412</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2526</v>
+        <v>-0.9198</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5856</v>
+        <v>0.1941</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4364</v>
+        <v>-0.2437</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1491</v>
+        <v>0.4378</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V. VINÓS ALTEMIR</t>
+          <t>R. RIU GARCIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0436</v>
+        <v>-3.2043</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7714</v>
+        <v>-1.2511</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2722</v>
+        <v>-1.9531</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2068</v>
+        <v>-1.5943</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1806</v>
+        <v>-0.9427</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3875</v>
+        <v>-0.6516</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7541</v>
+        <v>-1.0188</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2218</v>
+        <v>-0.6197</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5323</v>
+        <v>-0.3991</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9609</v>
+        <v>-0.5756</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0412</v>
+        <v>-0.323</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9198</v>
+        <v>-0.2526</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.861</v>
+        <v>-0.1375</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5498</v>
+        <v>-0.2324</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3112</v>
+        <v>0.0949</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>20.6144</v>
+        <v>22.655</v>
       </c>
       <c r="E24" t="n">
-        <v>17.16</v>
+        <v>17.1599</v>
       </c>
       <c r="F24" t="n">
-        <v>3.454599999999999</v>
+        <v>5.4953</v>
       </c>
       <c r="G24" t="n">
         <v>22.8993</v>
@@ -2326,13 +2326,13 @@
         <v>10.9111</v>
       </c>
       <c r="S24" t="n">
-        <v>1.6433</v>
+        <v>3.6839</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7362000000000002</v>
+        <v>-0.7363999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>2.3796</v>
+        <v>4.4202</v>
       </c>
       <c r="V24" t="n">
         <v>2.023600000000001</v>
